--- a/histograms/histogram_Valence_Electrons_Density_avg.xlsx
+++ b/histograms/histogram_Valence_Electrons_Density_avg.xlsx
@@ -442,15 +442,15 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02480463676651345</v>
+        <v>0.02459046932121763</v>
       </c>
       <c r="B2" t="n">
-        <v>160</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.03014219847448159</v>
+        <v>0.02949969613859412</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -458,146 +458,146 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.03547976018244972</v>
+        <v>0.03440892295597062</v>
       </c>
       <c r="B4" t="n">
-        <v>370</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.04081732189041786</v>
+        <v>0.03931814977334712</v>
       </c>
       <c r="B5" t="n">
-        <v>510</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.04615488359838599</v>
+        <v>0.04422737659072361</v>
       </c>
       <c r="B6" t="n">
-        <v>1475</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.05149244530635413</v>
+        <v>0.04913660340810011</v>
       </c>
       <c r="B7" t="n">
-        <v>291</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.05683000701432227</v>
+        <v>0.05404583022547661</v>
       </c>
       <c r="B8" t="n">
-        <v>2768</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.06216756872229041</v>
+        <v>0.0589550570428531</v>
       </c>
       <c r="B9" t="n">
-        <v>1177</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.06750513043025855</v>
+        <v>0.0638642838602296</v>
       </c>
       <c r="B10" t="n">
-        <v>1861</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.07284269213822668</v>
+        <v>0.06877351067760609</v>
       </c>
       <c r="B11" t="n">
-        <v>1771</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.07818025384619481</v>
+        <v>0.07368273749498258</v>
       </c>
       <c r="B12" t="n">
-        <v>4427</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.08351781555416296</v>
+        <v>0.0785919643123591</v>
       </c>
       <c r="B13" t="n">
-        <v>3686</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.08885537726213108</v>
+        <v>0.08350119112973559</v>
       </c>
       <c r="B14" t="n">
-        <v>2382</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.09419293897009923</v>
+        <v>0.08841041794711207</v>
       </c>
       <c r="B15" t="n">
-        <v>1594</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.09953050067806737</v>
+        <v>0.09331964476448858</v>
       </c>
       <c r="B16" t="n">
-        <v>1532</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.1048680623860355</v>
+        <v>0.09822887158186508</v>
       </c>
       <c r="B17" t="n">
-        <v>276</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.1102056240940036</v>
+        <v>0.1031380983992416</v>
       </c>
       <c r="B18" t="n">
-        <v>1756</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.1155431858019718</v>
+        <v>0.1080473252166181</v>
       </c>
       <c r="B19" t="n">
-        <v>128</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.1208807475099399</v>
+        <v>0.1129565520339946</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.1262183092179081</v>
+        <v>0.1178657788513711</v>
       </c>
       <c r="B21" t="n">
-        <v>235</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
